--- a/docs/deliverables/04_テスト/テスト実施報告書.xlsx
+++ b/docs/deliverables/04_テスト/テスト実施報告書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="Rc84efc0e4df94f26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="結論" sheetId="2" r:id="R6b0e4885b21149b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入テスト集計" sheetId="3" r:id="R86a1451e3212452b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実行した自動検査" sheetId="4" r:id="Rc1e8d5d6e94c491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブラウザー実機確認" sheetId="5" r:id="Rc971ebb80f0f40dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検出・修正した問題" sheetId="6" r:id="R9a2e6e95febb492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保留内容" sheetId="7" r:id="R0e5acd0ce1e04a4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式リリース判定条件" sheetId="8" r:id="Rc3105fd16e7c4ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R5ac85f0d6e514439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="結論" sheetId="2" r:id="R983015743f844401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入テスト集計" sheetId="3" r:id="R3a54c0a284174689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実行した自動検査" sheetId="4" r:id="R20a2de1ef7b24148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブラウザー実機確認" sheetId="5" r:id="Rae42884f9ebf42f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検出・修正した問題" sheetId="6" r:id="R9c36377bc44b45cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保留内容" sheetId="7" r:id="R72fa1429c8ae4515"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式リリース判定条件" sheetId="8" r:id="R0528076cdffd4dc0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1694,19 +1694,19 @@
         <x:v>•</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>管理者ログインと右上ユーザーID</x:v>
+        <x:v>管理者ログインと右上の氏名・所属部署表示</x:v>
       </x:c>
       <x:c r="C6" s="24" t="str">
-        <x:v>管理者ログインと右上ユーザーID</x:v>
+        <x:v>管理者ログインと右上の氏名・所属部署表示</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>管理者ログインと右上ユーザーID</x:v>
+        <x:v>管理者ログインと右上の氏名・所属部署表示</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str">
-        <x:v>管理者ログインと右上ユーザーID</x:v>
+        <x:v>管理者ログインと右上の氏名・所属部署表示</x:v>
       </x:c>
       <x:c r="F6" s="24" t="str">
-        <x:v>管理者ログインと右上ユーザーID</x:v>
+        <x:v>管理者ログインと右上の氏名・所属部署表示</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
